--- a/Configs/GameConfig/Datas/weapon_registry.xlsx
+++ b/Configs/GameConfig/Datas/weapon_registry.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03b1bc4bf23d416c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R12460a33b7584cdd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,24 +334,12 @@
       <x:c r="B1" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" t="str">
-        <x:v>symbol</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>type</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
-        <x:v>index</x:v>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>status</x:v>
-      </x:c>
-      <x:c r="H1" t="str">
-        <x:v>buffDependency</x:v>
-      </x:c>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -360,24 +348,12 @@
       <x:c r="B2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>string?</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>string?</x:v>
-      </x:c>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -396,44 +372,24 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>符号(主键)</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>名称</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>类型</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>索引</x:v>
-      </x:c>
-      <x:c r="G4" t="str">
-        <x:v>状态</x:v>
-      </x:c>
-      <x:c r="H4" t="str">
-        <x:v>Buff依赖</x:v>
-      </x:c>
+        <x:v>主键</x:v>
+      </x:c>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
       <x:c r="B5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>o5</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>虎啸战刀</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>hY</x:v>
-      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
       <x:c r="G5"/>
       <x:c r="H5"/>
     </x:row>
@@ -442,18 +398,10 @@
       <x:c r="B6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>qM</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>短刀</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
-        <x:v>hB</x:v>
-      </x:c>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
       <x:c r="G6"/>
       <x:c r="H6"/>
     </x:row>
@@ -462,18 +410,10 @@
       <x:c r="B7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>p1</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>短剑</x:v>
-      </x:c>
-      <x:c r="E7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>h1</x:v>
-      </x:c>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
       <x:c r="G7"/>
       <x:c r="H7"/>
     </x:row>
@@ -482,21 +422,11 @@
       <x:c r="B8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>ou</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>铁胎弓</x:v>
-      </x:c>
-      <x:c r="E8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
-        <x:v>DEFERRED_EFFECT_DEPENDENCY</x:v>
-      </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
       <x:c r="H8"/>
     </x:row>
     <x:row r="9">
@@ -504,18 +434,10 @@
       <x:c r="B9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>qq</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>梨花枪</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>hx</x:v>
-      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
       <x:c r="G9"/>
       <x:c r="H9"/>
     </x:row>
@@ -524,18 +446,10 @@
       <x:c r="B10" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>ni</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>青龙偃月刀</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>h0</x:v>
-      </x:c>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
       <x:c r="G10"/>
       <x:c r="H10"/>
     </x:row>
@@ -544,18 +458,10 @@
       <x:c r="B11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>rI</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>虎头湛金枪</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
-        <x:v>hy</x:v>
-      </x:c>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
       <x:c r="G11"/>
       <x:c r="H11"/>
     </x:row>
@@ -564,45 +470,23 @@
       <x:c r="B12" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C12" t="str">
-        <x:v>sM</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>长弓</x:v>
-      </x:c>
-      <x:c r="E12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>COMPLETE_FOR_LOGIC_NO_ASSETS</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>RESOLVED</x:v>
-      </x:c>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
       <x:c r="B13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C13" t="str">
-        <x:v>tr</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>霸王弓</x:v>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>PARTIAL_WITH_EXACT_GAPS</x:v>
-      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
       <x:c r="H13"/>
     </x:row>
     <x:row r="14">
@@ -610,18 +494,10 @@
       <x:c r="B14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C14" t="str">
-        <x:v>sN</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>铁剑</x:v>
-      </x:c>
-      <x:c r="E14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>hN</x:v>
-      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
       <x:c r="G14"/>
       <x:c r="H14"/>
     </x:row>
@@ -630,18 +506,10 @@
       <x:c r="B15" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C15" t="str">
-        <x:v>qF</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>龙渊剑</x:v>
-      </x:c>
-      <x:c r="E15" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>h8</x:v>
-      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
       <x:c r="G15"/>
       <x:c r="H15"/>
     </x:row>
@@ -650,18 +518,10 @@
       <x:c r="B16" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C16" t="str">
-        <x:v>tC</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>莫邪</x:v>
-      </x:c>
-      <x:c r="E16" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F16" t="str">
-        <x:v>hJ</x:v>
-      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
       <x:c r="G16"/>
       <x:c r="H16"/>
     </x:row>
@@ -670,42 +530,22 @@
       <x:c r="B17" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" t="str">
-        <x:v>sg</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>角弓</x:v>
-      </x:c>
-      <x:c r="E17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G17" t="str">
-        <x:v>COMPLETE_FOR_LOGIC_NO_ASSETS</x:v>
-      </x:c>
-      <x:c r="H17" t="str">
-        <x:v>RESOLVED</x:v>
-      </x:c>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18"/>
       <x:c r="B18" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" t="str">
-        <x:v>o2</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>长剑</x:v>
-      </x:c>
-      <x:c r="E18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F18" t="str">
-        <x:v>h2</x:v>
-      </x:c>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
       <x:c r="G18"/>
       <x:c r="H18"/>
     </x:row>
@@ -714,18 +554,10 @@
       <x:c r="B19" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" t="str">
-        <x:v>oy</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>钩镰枪</x:v>
-      </x:c>
-      <x:c r="E19" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F19" t="str">
-        <x:v>hv</x:v>
-      </x:c>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
       <x:c r="G19"/>
       <x:c r="H19"/>
     </x:row>
@@ -734,18 +566,10 @@
       <x:c r="B20" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C20" t="str">
-        <x:v>pd</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>三尖刀</x:v>
-      </x:c>
-      <x:c r="E20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F20" t="str">
-        <x:v>hF</x:v>
-      </x:c>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
       <x:c r="G20"/>
       <x:c r="H20"/>
     </x:row>
@@ -754,18 +578,10 @@
       <x:c r="B21" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C21" t="str">
-        <x:v>sx</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>古锭刀</x:v>
-      </x:c>
-      <x:c r="E21" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F21" t="str">
-        <x:v>hV</x:v>
-      </x:c>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
       <x:c r="G21"/>
       <x:c r="H21"/>
     </x:row>
@@ -774,18 +590,10 @@
       <x:c r="B22" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C22" t="str">
-        <x:v>oM</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>七星剑</x:v>
-      </x:c>
-      <x:c r="E22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>ib</x:v>
-      </x:c>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
       <x:c r="G22"/>
       <x:c r="H22"/>
     </x:row>
@@ -794,18 +602,10 @@
       <x:c r="B23" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C23" t="str">
-        <x:v>tU</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>丈八蛇矛</x:v>
-      </x:c>
-      <x:c r="E23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F23" t="str">
-        <x:v>hz</x:v>
-      </x:c>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
       <x:c r="G23"/>
       <x:c r="H23"/>
     </x:row>
@@ -814,18 +614,10 @@
       <x:c r="B24" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C24" t="str">
-        <x:v>pL</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>方天画戟</x:v>
-      </x:c>
-      <x:c r="E24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F24" t="str">
-        <x:v>hL</x:v>
-      </x:c>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
       <x:c r="G24"/>
       <x:c r="H24"/>
     </x:row>
@@ -834,18 +626,10 @@
       <x:c r="B25" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C25" t="str">
-        <x:v>oD</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>巨阙剑</x:v>
-      </x:c>
-      <x:c r="E25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F25" t="str">
-        <x:v>h3</x:v>
-      </x:c>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
       <x:c r="G25"/>
       <x:c r="H25"/>
     </x:row>
@@ -854,18 +638,10 @@
       <x:c r="B26" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C26" t="str">
-        <x:v>o6</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>大戟</x:v>
-      </x:c>
-      <x:c r="E26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F26" t="str">
-        <x:v>hs</x:v>
-      </x:c>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
       <x:c r="G26"/>
       <x:c r="H26"/>
     </x:row>
@@ -874,18 +650,10 @@
       <x:c r="B27" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C27" t="str">
-        <x:v>pK</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>狼牙棒</x:v>
-      </x:c>
-      <x:c r="E27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F27" t="str">
-        <x:v>hE</x:v>
-      </x:c>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
       <x:c r="G27"/>
       <x:c r="H27"/>
     </x:row>
@@ -894,18 +662,10 @@
       <x:c r="B28" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C28" t="str">
-        <x:v>qQ</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>铁刀</x:v>
-      </x:c>
-      <x:c r="E28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F28" t="str">
-        <x:v>hD</x:v>
-      </x:c>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
       <x:c r="G28"/>
       <x:c r="H28"/>
     </x:row>
@@ -914,18 +674,10 @@
       <x:c r="B29" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C29" t="str">
-        <x:v>rq</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>轩辕剑</x:v>
-      </x:c>
-      <x:c r="E29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F29" t="str">
-        <x:v>ie</x:v>
-      </x:c>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
       <x:c r="G29"/>
       <x:c r="H29"/>
     </x:row>
@@ -934,42 +686,22 @@
       <x:c r="B30" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C30" t="str">
-        <x:v>pO</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>落日弓</x:v>
-      </x:c>
-      <x:c r="E30" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F30" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G30" t="str">
-        <x:v>PARTIAL_WITH_EXACT_GAPS</x:v>
-      </x:c>
-      <x:c r="H30" t="str">
-        <x:v>RESOLVED</x:v>
-      </x:c>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31"/>
       <x:c r="B31" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C31" t="str">
-        <x:v>sT</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>青钢剑</x:v>
-      </x:c>
-      <x:c r="E31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F31" t="str">
-        <x:v>ia</x:v>
-      </x:c>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
       <x:c r="G31"/>
       <x:c r="H31"/>
     </x:row>
@@ -978,18 +710,10 @@
       <x:c r="B32" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C32" t="str">
-        <x:v>qp</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
-        <x:v>龙泉剑</x:v>
-      </x:c>
-      <x:c r="E32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F32" t="str">
-        <x:v>h4</x:v>
-      </x:c>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
       <x:c r="G32"/>
       <x:c r="H32"/>
     </x:row>
@@ -998,42 +722,22 @@
       <x:c r="B33" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C33" t="str">
-        <x:v>rQ</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
-        <x:v>神臂弓</x:v>
-      </x:c>
-      <x:c r="E33" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F33" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G33" t="str">
-        <x:v>COMPLETE_FOR_LOGIC_NO_ASSETS</x:v>
-      </x:c>
-      <x:c r="H33" t="str">
-        <x:v>RESOLVED</x:v>
-      </x:c>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
       <x:c r="B34" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C34" t="str">
-        <x:v>pq</x:v>
-      </x:c>
-      <x:c r="D34" t="str">
-        <x:v>七星刀</x:v>
-      </x:c>
-      <x:c r="E34" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F34" t="str">
-        <x:v>hZ</x:v>
-      </x:c>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
       <x:c r="G34"/>
       <x:c r="H34"/>
     </x:row>
@@ -1042,18 +746,10 @@
       <x:c r="B35" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C35" t="str">
-        <x:v>rL</x:v>
-      </x:c>
-      <x:c r="D35" t="str">
-        <x:v>双股剑</x:v>
-      </x:c>
-      <x:c r="E35" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F35" t="str">
-        <x:v>h9</x:v>
-      </x:c>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
       <x:c r="G35"/>
       <x:c r="H35"/>
     </x:row>
@@ -1062,18 +758,10 @@
       <x:c r="B36" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C36" t="str">
-        <x:v>n3</x:v>
-      </x:c>
-      <x:c r="D36" t="str">
-        <x:v>铁枪</x:v>
-      </x:c>
-      <x:c r="E36" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F36" t="str">
-        <x:v>hq</x:v>
-      </x:c>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
       <x:c r="G36"/>
       <x:c r="H36"/>
     </x:row>
@@ -1082,18 +770,10 @@
       <x:c r="B37" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C37" t="str">
-        <x:v>su</x:v>
-      </x:c>
-      <x:c r="D37" t="str">
-        <x:v>木刀</x:v>
-      </x:c>
-      <x:c r="E37" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F37" t="str">
-        <x:v>-1</x:v>
-      </x:c>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
       <x:c r="G37"/>
       <x:c r="H37"/>
     </x:row>
@@ -1102,18 +782,10 @@
       <x:c r="B38" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C38" t="str">
-        <x:v>pz</x:v>
-      </x:c>
-      <x:c r="D38" t="str">
-        <x:v>龙胆亮银枪</x:v>
-      </x:c>
-      <x:c r="E38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F38" t="str">
-        <x:v>hA</x:v>
-      </x:c>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
       <x:c r="G38"/>
       <x:c r="H38"/>
     </x:row>
@@ -1122,18 +794,10 @@
       <x:c r="B39" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C39" t="str">
-        <x:v>oB</x:v>
-      </x:c>
-      <x:c r="D39" t="str">
-        <x:v>长刀</x:v>
-      </x:c>
-      <x:c r="E39" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F39" t="str">
-        <x:v>hC</x:v>
-      </x:c>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
       <x:c r="G39"/>
       <x:c r="H39"/>
     </x:row>
@@ -1142,18 +806,10 @@
       <x:c r="B40" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C40" t="str">
-        <x:v>nl</x:v>
-      </x:c>
-      <x:c r="D40" t="str">
-        <x:v>长枪</x:v>
-      </x:c>
-      <x:c r="E40" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F40" t="str">
-        <x:v>hp</x:v>
-      </x:c>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
       <x:c r="G40"/>
       <x:c r="H40"/>
     </x:row>
@@ -1162,21 +818,11 @@
       <x:c r="B41" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C41" t="str">
-        <x:v>pr</x:v>
-      </x:c>
-      <x:c r="D41" t="str">
-        <x:v>铁弓</x:v>
-      </x:c>
-      <x:c r="E41" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F41" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G41" t="str">
-        <x:v>DEFERRED_EFFECT_DEPENDENCY</x:v>
-      </x:c>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
+      <x:c r="E41"/>
+      <x:c r="F41"/>
+      <x:c r="G41"/>
       <x:c r="H41"/>
     </x:row>
     <x:row r="42">
@@ -1184,18 +830,10 @@
       <x:c r="B42" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C42" t="str">
-        <x:v>pY</x:v>
-      </x:c>
-      <x:c r="D42" t="str">
-        <x:v>点钢枪</x:v>
-      </x:c>
-      <x:c r="E42" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F42" t="str">
-        <x:v>hw</x:v>
-      </x:c>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
       <x:c r="G42"/>
       <x:c r="H42"/>
     </x:row>
@@ -1204,18 +842,10 @@
       <x:c r="B43" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C43" t="str">
-        <x:v>pv</x:v>
-      </x:c>
-      <x:c r="D43" t="str">
-        <x:v>倚天剑</x:v>
-      </x:c>
-      <x:c r="E43" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F43" t="str">
-        <x:v>ic</x:v>
-      </x:c>
+      <x:c r="C43"/>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
+      <x:c r="F43"/>
       <x:c r="G43"/>
       <x:c r="H43"/>
     </x:row>
@@ -1224,18 +854,10 @@
       <x:c r="B44" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C44" t="str">
-        <x:v>oV</x:v>
-      </x:c>
-      <x:c r="D44" t="str">
-        <x:v>铁蒺藜骨朵</x:v>
-      </x:c>
-      <x:c r="E44" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F44" t="str">
-        <x:v>hU</x:v>
-      </x:c>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
       <x:c r="G44"/>
       <x:c r="H44"/>
     </x:row>
@@ -1244,21 +866,11 @@
       <x:c r="B45" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C45" t="str">
-        <x:v>qG</x:v>
-      </x:c>
-      <x:c r="D45" t="str">
-        <x:v>诸葛连弩</x:v>
-      </x:c>
-      <x:c r="E45" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F45" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G45" t="str">
-        <x:v>PARTIAL_WITH_EXACT_GAPS</x:v>
-      </x:c>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+      <x:c r="G45"/>
       <x:c r="H45"/>
     </x:row>
     <x:row r="46">
@@ -1266,18 +878,10 @@
       <x:c r="B46" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C46" t="str">
-        <x:v>pg</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
-        <x:v>干将</x:v>
-      </x:c>
-      <x:c r="E46" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F46" t="str">
-        <x:v>id</x:v>
-      </x:c>
+      <x:c r="C46"/>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
       <x:c r="G46"/>
       <x:c r="H46"/>
     </x:row>
@@ -1286,21 +890,11 @@
       <x:c r="B47" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C47" t="str">
-        <x:v>rG</x:v>
-      </x:c>
-      <x:c r="D47" t="str">
-        <x:v>射雕弓</x:v>
-      </x:c>
-      <x:c r="E47" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F47" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G47" t="str">
-        <x:v>COMPLETE_FOR_LOGIC_NO_ASSETS</x:v>
-      </x:c>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
       <x:c r="H47"/>
     </x:row>
     <x:row r="48">
@@ -1308,18 +902,10 @@
       <x:c r="B48" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C48" t="str">
-        <x:v>tt</x:v>
-      </x:c>
-      <x:c r="D48" t="str">
-        <x:v>短枪</x:v>
-      </x:c>
-      <x:c r="E48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F48" t="str">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
       <x:c r="G48"/>
       <x:c r="H48"/>
     </x:row>
